--- a/outputs/monitor_xlsx/20260319.xlsx
+++ b/outputs/monitor_xlsx/20260319.xlsx
@@ -544,10 +544,6 @@
           <t>+0.49%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-4.91%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+0.45%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>+0.87%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>-4.11%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>-2.16%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -695,7 +671,6 @@
           <t>-909.48億</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>-366.59億</t>
@@ -733,7 +708,6 @@
           <t>-3.46億</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>-0.29億</t>
@@ -744,8 +718,6 @@
           <t>-1.47億</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -763,15 +735,11 @@
           <t>109.58%</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>142.42%</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -789,11 +757,6 @@
           <t>-1024.27億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -811,15 +774,11 @@
           <t>12285口</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>14397口</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,7 +796,6 @@
           <t>-26.0億</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>-49.18億</t>
@@ -942,10 +900,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1067,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1102,6 +1056,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2224,6 +2179,106 @@
       <c r="W20" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>7210</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="E21" t="n">
+        <v>570</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G21" t="n">
+        <v>177</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-31</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-32</v>
+      </c>
+      <c r="J21" t="n">
+        <v>21</v>
+      </c>
+      <c r="K21" t="n">
+        <v>265</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1274</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-8982</v>
+      </c>
+      <c r="N21" t="n">
+        <v>31.44</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1595</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4711</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>-944</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-1926</v>
+      </c>
+      <c r="H22" t="n">
+        <v>137</v>
+      </c>
+      <c r="I22" t="n">
+        <v>782</v>
+      </c>
+      <c r="J22" t="n">
+        <v>56</v>
+      </c>
+      <c r="L22" t="n">
+        <v>13160</v>
+      </c>
+      <c r="N22" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260319.xlsx
+++ b/outputs/monitor_xlsx/20260319.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -526,220 +526,232 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>美債10年殖利率</t>
+          <t>加權指數 (TWII)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.28%</t>
+          <t>33689.68</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+0.49%</t>
-        </is>
-      </c>
+          <t>-1.92%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>黃金指數 (GC=F)</t>
+          <t>櫃買指數 (OTC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4650.0$</t>
+          <t>329.79</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-4.91%</t>
-        </is>
-      </c>
+          <t>+0.12%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>貨幣</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>美元/台幣匯率</t>
+          <t>台指近月期貨</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>32.03</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+0.45%</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>現貨</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>費半指數 (SOX)</t>
+          <t>美債10年殖利率</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7863.3</t>
+          <t>4.28%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+0.87%</t>
-        </is>
-      </c>
+          <t>+0.49%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>情緒</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>恐慌指數 (VIX)</t>
+          <t>黃金指數 (GC=F)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>24.06</t>
+          <t>4600.7$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-4.11%</t>
-        </is>
-      </c>
+          <t>-5.91%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>原物料</t>
+          <t>貨幣</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WTI原油期貨</t>
+          <t>美元/台幣匯率</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>94.24$</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-2.16%</t>
-        </is>
-      </c>
+          <t>+0.45%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>現貨</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>外資現貨</t>
+          <t>費半指數 (SOX)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-909.48億</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-366.59億</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-1832.97億</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-235.22億</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-4704.5億</t>
-        </is>
-      </c>
+          <t>7863.3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>+0.87%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>情緒</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>投信現貨</t>
+          <t>恐慌指數 (VIX)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.46億</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>-0.29億</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-1.47億</t>
-        </is>
-      </c>
+          <t>24.06</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-4.11%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>原物料</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>選擇權 P/C Ratio</t>
+          <t>WTI原油期貨</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>109.58%</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>142.42%</t>
-        </is>
-      </c>
+          <t>96.14$</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-0.19%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -749,12 +761,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>三大法人合計</t>
+          <t>外資現貨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1024.27億</t>
+          <t>-909.48億</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-509.79億</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-2548.97億</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>None億</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -766,54 +799,137 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>外資期貨未平倉</t>
+          <t>投信現貨</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12285口</t>
-        </is>
-      </c>
+          <t>-3.46億</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14397口</t>
-        </is>
-      </c>
+          <t>-2.21億</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-11.05億</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>選擇權 P/C Ratio</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>142.42%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>三大法人合計</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-1024.27億</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>外資期貨未平倉</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>12285口</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>14397口</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>結算</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>融資融券變化</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>-26.0億</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>-49.18億</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>-245.89億</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-19.4億</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-388.08億</t>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>None億</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -860,7 +976,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-366.59億</t>
+          <t>-509.79億</t>
         </is>
       </c>
     </row>
@@ -872,7 +988,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1832.97億</t>
+          <t>-2548.97億</t>
         </is>
       </c>
     </row>
@@ -884,7 +1000,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-235.22億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -896,9 +1012,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-4704.5億</t>
-        </is>
-      </c>
+          <t>None億</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -908,7 +1028,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-0.29億</t>
+          <t>-2.21億</t>
         </is>
       </c>
     </row>
@@ -920,7 +1040,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-1.47億</t>
+          <t>-11.05億</t>
         </is>
       </c>
     </row>
@@ -963,7 +1083,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-19.4億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -975,7 +1095,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-388.08億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1039,14 +1159,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1056,7 +1175,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1135,40 +1253,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1220,12 +1333,7 @@
       <c r="N4" t="n">
         <v>-4479016</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1280,12 +1388,7 @@
       <c r="N5" t="n">
         <v>-78831</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1340,12 +1443,7 @@
       <c r="N6" t="n">
         <v>-649175</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1400,12 +1498,7 @@
       <c r="N7" t="n">
         <v>-6483124</v>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1414,12 +1507,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1428,44 +1521,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>122</v>
+        <v>1590</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-4.69</v>
+        <v>-0.62</v>
       </c>
       <c r="F8" t="n">
-        <v>198121</v>
+        <v>7188</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>-36072</v>
+        <v>-126</v>
       </c>
       <c r="H8" t="n">
-        <v>61007</v>
+        <v>-1576</v>
       </c>
       <c r="I8" t="n">
-        <v>-585</v>
+        <v>246</v>
       </c>
       <c r="J8" t="n">
-        <v>534</v>
+        <v>-458</v>
       </c>
       <c r="K8" t="n">
-        <v>2480</v>
+        <v>188</v>
       </c>
       <c r="L8" t="n">
-        <v>135580</v>
+        <v>2250</v>
       </c>
       <c r="M8" t="n">
-        <v>521145</v>
+        <v>8752</v>
       </c>
       <c r="N8" t="n">
-        <v>-1117853</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>-140167</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1474,12 +1562,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1488,44 +1576,39 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2890</v>
+        <v>1595</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7.04</v>
+        <v>1.92</v>
       </c>
       <c r="F9" t="n">
-        <v>5842</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>764</v>
+        <v>4711</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>-944</v>
       </c>
       <c r="H9" t="n">
-        <v>-1409</v>
+        <v>-982</v>
       </c>
       <c r="I9" t="n">
-        <v>-54</v>
+        <v>137</v>
       </c>
       <c r="J9" t="n">
-        <v>38</v>
+        <v>645</v>
       </c>
       <c r="K9" t="n">
-        <v>277</v>
+        <v>56</v>
       </c>
       <c r="L9" t="n">
-        <v>1848</v>
+        <v>3464</v>
       </c>
       <c r="M9" t="n">
-        <v>7921</v>
+        <v>13160</v>
       </c>
       <c r="N9" t="n">
-        <v>-89526</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>-106285</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1534,12 +1617,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1548,44 +1631,39 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3220</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>-2.42</v>
+        <v>2890</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>7.04</v>
       </c>
       <c r="F10" t="n">
-        <v>1827</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>-183</v>
+        <v>5842</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>764</v>
       </c>
       <c r="H10" t="n">
-        <v>150</v>
+        <v>-1409</v>
       </c>
       <c r="I10" t="n">
-        <v>-97</v>
+        <v>-54</v>
       </c>
       <c r="J10" t="n">
-        <v>-384</v>
+        <v>38</v>
       </c>
       <c r="K10" t="n">
-        <v>72</v>
+        <v>277</v>
       </c>
       <c r="L10" t="n">
-        <v>5837</v>
+        <v>1848</v>
       </c>
       <c r="M10" t="n">
-        <v>23089</v>
+        <v>7921</v>
       </c>
       <c r="N10" t="n">
-        <v>-19753</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+        <v>-89526</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1640,12 +1718,7 @@
       <c r="N11" t="n">
         <v>-19447</v>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1654,58 +1727,53 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1540</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>6.94</v>
+        <v>7210</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>-0.14</v>
       </c>
       <c r="F12" t="n">
-        <v>549</v>
+        <v>570</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="H12" t="n">
-        <v>362</v>
+        <v>138</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>-31</v>
       </c>
       <c r="J12" t="n">
-        <v>20</v>
+        <v>-1</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="L12" t="n">
-        <v>-42</v>
+        <v>265</v>
       </c>
       <c r="M12" t="n">
-        <v>-662</v>
+        <v>1009</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8982</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1714,12 +1782,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1728,44 +1796,39 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>391.5</v>
+        <v>2315</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>2.22</v>
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>25881</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>-284</v>
+        <v>2730</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>116</v>
       </c>
       <c r="H13" t="n">
-        <v>-4983</v>
+        <v>362</v>
       </c>
       <c r="I13" t="n">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>-4772</v>
+        <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13" t="n">
-        <v>33</v>
+        <v>-42</v>
       </c>
       <c r="M13" t="n">
-        <v>1485</v>
+        <v>-662</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1774,12 +1837,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1788,41 +1851,39 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1400</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>-2.44</v>
+        <v>449.5</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>446</v>
+        <v>3871</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>-58</v>
+        <v>-284</v>
       </c>
       <c r="H14" t="n">
-        <v>-163</v>
+        <v>-4983</v>
+      </c>
+      <c r="I14" t="n">
+        <v>67</v>
       </c>
       <c r="J14" t="n">
-        <v>25</v>
+        <v>-4772</v>
       </c>
       <c r="K14" t="n">
-        <v>23</v>
+        <v>-1</v>
       </c>
       <c r="L14" t="n">
-        <v>-7</v>
+        <v>33</v>
       </c>
       <c r="M14" t="n">
-        <v>-94</v>
+        <v>1485</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1831,58 +1892,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1590</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>-0.62</v>
+        <v>974</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>7188</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>-126</v>
+        <v>1350</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>303</v>
       </c>
       <c r="H15" t="n">
-        <v>-1576</v>
-      </c>
-      <c r="I15" t="n">
-        <v>246</v>
+        <v>614</v>
       </c>
       <c r="J15" t="n">
-        <v>-458</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>188</v>
+        <v>12</v>
       </c>
       <c r="L15" t="n">
-        <v>2250</v>
+        <v>-105</v>
       </c>
       <c r="M15" t="n">
-        <v>8752</v>
+        <v>-115</v>
       </c>
       <c r="N15" t="n">
-        <v>-140167</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1891,12 +1944,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1905,380 +1958,38 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>918</v>
+        <v>1600</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>3.38</v>
+        <v>4.92</v>
       </c>
       <c r="F16" t="n">
-        <v>759</v>
+        <v>904</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="H16" t="n">
-        <v>-2723</v>
-      </c>
-      <c r="I16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="J16" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>65</v>
+        <v>-11</v>
       </c>
       <c r="L16" t="n">
-        <v>-91</v>
+        <v>-49</v>
       </c>
       <c r="M16" t="n">
-        <v>1263</v>
+        <v>316</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>漢唐</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>915</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>-2.45</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2939</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>-952</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-6208</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-451</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-1098</v>
-      </c>
-      <c r="K17" t="n">
-        <v>255</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2801</v>
-      </c>
-      <c r="M17" t="n">
-        <v>9672</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-47632</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>6640</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>均豪</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1095</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>-1.35</v>
-      </c>
-      <c r="F18" t="n">
-        <v>605</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="H18" t="n">
-        <v>67</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-49</v>
-      </c>
-      <c r="M18" t="n">
-        <v>316</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>745</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1862</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>303</v>
-      </c>
-      <c r="H19" t="n">
-        <v>614</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>12</v>
-      </c>
-      <c r="L19" t="n">
-        <v>-105</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-115</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3030</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>德律</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>263.5</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="F20" t="n">
-        <v>5706</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>-459</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-1811</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J20" t="n">
-        <v>80</v>
-      </c>
-      <c r="K20" t="n">
-        <v>149</v>
-      </c>
-      <c r="L20" t="n">
-        <v>7280</v>
-      </c>
-      <c r="M20" t="n">
-        <v>28385</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-58939</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>7210</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="E21" t="n">
-        <v>570</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="G21" t="n">
-        <v>177</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-31</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-32</v>
-      </c>
-      <c r="J21" t="n">
-        <v>21</v>
-      </c>
-      <c r="K21" t="n">
-        <v>265</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1274</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-8982</v>
-      </c>
-      <c r="N21" t="n">
-        <v>31.44</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1595</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="E22" t="n">
-        <v>4711</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>-944</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-1926</v>
-      </c>
-      <c r="H22" t="n">
-        <v>137</v>
-      </c>
-      <c r="I22" t="n">
-        <v>782</v>
-      </c>
-      <c r="J22" t="n">
-        <v>56</v>
-      </c>
-      <c r="L22" t="n">
-        <v>13160</v>
-      </c>
-      <c r="N22" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260319.xlsx
+++ b/outputs/monitor_xlsx/20260319.xlsx
@@ -544,10 +544,6 @@
           <t>-1.92%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+0.12%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,11 +583,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -618,10 +605,6 @@
           <t>+0.49%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,10 +627,6 @@
           <t>-5.91%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,10 +649,6 @@
           <t>+0.45%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -696,10 +671,6 @@
           <t>+0.87%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,10 +693,6 @@
           <t>-4.11%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -748,10 +715,6 @@
           <t>-0.19%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -769,7 +732,6 @@
           <t>-909.48億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-509.79億</t>
@@ -807,7 +769,6 @@
           <t>-3.46億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>-2.21億</t>
@@ -818,8 +779,6 @@
           <t>-11.05億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,15 +796,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>142.42%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,11 +818,6 @@
           <t>-1024.27億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -885,15 +835,11 @@
           <t>12285口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>14397口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -911,7 +857,6 @@
           <t>-26.0億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-49.18億</t>
@@ -1016,10 +961,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1141,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1175,6 +1117,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1991,6 +1934,54 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>357</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="E17" t="n">
+        <v>812</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-1853</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>589</v>
+      </c>
+      <c r="J17" t="n">
+        <v>18</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8637</v>
+      </c>
+      <c r="L17" t="n">
+        <v>43342</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-22111</v>
+      </c>
+      <c r="N17" t="n">
+        <v>16.2</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260319.xlsx
+++ b/outputs/monitor_xlsx/20260319.xlsx
@@ -961,7 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1238,7 +1237,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1246,20 +1245,23 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>76</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>-2.31</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>141733</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>-89171</v>
       </c>
       <c r="H4" t="n">
-        <v>-130959</v>
+        <v>-220130</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>8679</v>
@@ -1271,11 +1273,14 @@
         <v>13170</v>
       </c>
       <c r="M4" t="n">
-        <v>53350</v>
+        <v>66520</v>
       </c>
       <c r="N4" t="n">
         <v>-4479016</v>
       </c>
+      <c r="O4" t="n">
+        <v>-1.7</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1298,26 +1303,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>922</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>-0.75</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="6" t="n">
         <v>1714</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>31</v>
       </c>
       <c r="H5" t="n">
-        <v>-449</v>
+        <v>-418</v>
       </c>
       <c r="I5" t="n">
         <v>-24</v>
       </c>
       <c r="J5" t="n">
-        <v>-188</v>
+        <v>-212</v>
       </c>
       <c r="K5" t="n">
         <v>39</v>
@@ -1326,11 +1331,14 @@
         <v>2885</v>
       </c>
       <c r="M5" t="n">
-        <v>11404</v>
+        <v>14289</v>
       </c>
       <c r="N5" t="n">
         <v>-78831</v>
       </c>
+      <c r="O5" t="n">
+        <v>-3.02</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1353,26 +1361,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1455</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>-0.68</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="6" t="n">
         <v>8335</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1193</v>
       </c>
       <c r="H6" t="n">
-        <v>4851</v>
+        <v>6044</v>
       </c>
       <c r="I6" t="n">
         <v>-126</v>
       </c>
       <c r="J6" t="n">
-        <v>-610</v>
+        <v>-736</v>
       </c>
       <c r="K6" t="n">
         <v>116</v>
@@ -1381,11 +1389,14 @@
         <v>5292</v>
       </c>
       <c r="M6" t="n">
-        <v>22862</v>
+        <v>28154</v>
       </c>
       <c r="N6" t="n">
         <v>-649175</v>
       </c>
+      <c r="O6" t="n">
+        <v>7.54</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1408,26 +1419,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1850</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>-2.89</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>38750</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>-22790</v>
       </c>
       <c r="H7" t="n">
-        <v>-28774</v>
+        <v>-51564</v>
       </c>
       <c r="I7" t="n">
         <v>-100</v>
       </c>
       <c r="J7" t="n">
-        <v>-1572</v>
+        <v>-1671</v>
       </c>
       <c r="K7" t="n">
         <v>371</v>
@@ -1436,11 +1447,14 @@
         <v>26269</v>
       </c>
       <c r="M7" t="n">
-        <v>101870</v>
+        <v>128139</v>
       </c>
       <c r="N7" t="n">
         <v>-6483124</v>
       </c>
+      <c r="O7" t="n">
+        <v>-2.77</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1463,26 +1477,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1590</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>-0.62</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>7188</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>-126</v>
       </c>
       <c r="H8" t="n">
-        <v>-1576</v>
+        <v>-1703</v>
       </c>
       <c r="I8" t="n">
         <v>246</v>
       </c>
       <c r="J8" t="n">
-        <v>-458</v>
+        <v>-213</v>
       </c>
       <c r="K8" t="n">
         <v>188</v>
@@ -1491,11 +1505,14 @@
         <v>2250</v>
       </c>
       <c r="M8" t="n">
-        <v>8752</v>
+        <v>11002</v>
       </c>
       <c r="N8" t="n">
         <v>-140167</v>
       </c>
+      <c r="O8" t="n">
+        <v>10.49</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1518,26 +1535,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="7" t="n">
         <v>1595</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>1.92</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>4711</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>-944</v>
       </c>
       <c r="H9" t="n">
-        <v>-982</v>
+        <v>-1926</v>
       </c>
       <c r="I9" t="n">
         <v>137</v>
       </c>
       <c r="J9" t="n">
-        <v>645</v>
+        <v>782</v>
       </c>
       <c r="K9" t="n">
         <v>56</v>
@@ -1546,11 +1563,14 @@
         <v>3464</v>
       </c>
       <c r="M9" t="n">
-        <v>13160</v>
+        <v>16624</v>
       </c>
       <c r="N9" t="n">
         <v>-106285</v>
       </c>
+      <c r="O9" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1573,26 +1593,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="7" t="n">
         <v>2890</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>7.04</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="6" t="n">
         <v>5842</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>764</v>
       </c>
       <c r="H10" t="n">
-        <v>-1409</v>
+        <v>-646</v>
       </c>
       <c r="I10" t="n">
         <v>-54</v>
       </c>
       <c r="J10" t="n">
-        <v>38</v>
+        <v>-16</v>
       </c>
       <c r="K10" t="n">
         <v>277</v>
@@ -1601,11 +1621,14 @@
         <v>1848</v>
       </c>
       <c r="M10" t="n">
-        <v>7921</v>
+        <v>9769</v>
       </c>
       <c r="N10" t="n">
         <v>-89526</v>
       </c>
+      <c r="O10" t="n">
+        <v>19.32</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1628,26 +1651,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="7" t="n">
         <v>1930</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>4.32</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="6" t="n">
         <v>518</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="I11" t="n">
         <v>43</v>
       </c>
       <c r="J11" t="n">
-        <v>-93</v>
+        <v>-50</v>
       </c>
       <c r="K11" t="n">
         <v>33</v>
@@ -1656,11 +1679,14 @@
         <v>4107</v>
       </c>
       <c r="M11" t="n">
-        <v>17071</v>
+        <v>21178</v>
       </c>
       <c r="N11" t="n">
         <v>-19447</v>
       </c>
+      <c r="O11" t="n">
+        <v>-0.25</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1683,26 +1709,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>7210</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>-0.14</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="6" t="n">
         <v>570</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>40</v>
       </c>
       <c r="H12" t="n">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="I12" t="n">
         <v>-31</v>
       </c>
       <c r="J12" t="n">
-        <v>-1</v>
+        <v>-32</v>
       </c>
       <c r="K12" t="n">
         <v>21</v>
@@ -1711,11 +1737,14 @@
         <v>265</v>
       </c>
       <c r="M12" t="n">
-        <v>1009</v>
+        <v>1274</v>
       </c>
       <c r="N12" t="n">
         <v>-8982</v>
       </c>
+      <c r="O12" t="n">
+        <v>31.44</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1738,26 +1767,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="7" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>116</v>
       </c>
       <c r="H13" t="n">
-        <v>362</v>
+        <v>478</v>
       </c>
       <c r="I13" t="n">
         <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K13" t="n">
         <v>8</v>
@@ -1766,11 +1795,14 @@
         <v>-42</v>
       </c>
       <c r="M13" t="n">
-        <v>-662</v>
+        <v>-704</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1793,26 +1825,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="7" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>-284</v>
       </c>
       <c r="H14" t="n">
-        <v>-4983</v>
+        <v>-5267</v>
       </c>
       <c r="I14" t="n">
         <v>67</v>
       </c>
       <c r="J14" t="n">
-        <v>-4772</v>
+        <v>-4705</v>
       </c>
       <c r="K14" t="n">
         <v>-1</v>
@@ -1821,11 +1853,14 @@
         <v>33</v>
       </c>
       <c r="M14" t="n">
-        <v>1485</v>
+        <v>1518</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1848,20 +1883,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="6" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>303</v>
       </c>
       <c r="H15" t="n">
-        <v>614</v>
+        <v>917</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1873,11 +1911,14 @@
         <v>-105</v>
       </c>
       <c r="M15" t="n">
-        <v>-115</v>
+        <v>-220</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1900,20 +1941,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="6" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>120</v>
       </c>
       <c r="H16" t="n">
-        <v>67</v>
+        <v>187</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1925,11 +1969,14 @@
         <v>-49</v>
       </c>
       <c r="M16" t="n">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1947,41 +1994,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
         <v>357</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="E17" s="7" t="n">
         <v>2.29</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="6" t="n">
         <v>812</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G17" t="n">
-        <v>-1853</v>
-      </c>
       <c r="H17" t="n">
+        <v>-1297</v>
+      </c>
+      <c r="I17" t="n">
         <v>-3</v>
       </c>
-      <c r="I17" t="n">
-        <v>589</v>
-      </c>
       <c r="J17" t="n">
+        <v>690</v>
+      </c>
+      <c r="K17" t="n">
         <v>18</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>8637</v>
       </c>
-      <c r="L17" t="n">
-        <v>43342</v>
-      </c>
       <c r="M17" t="n">
+        <v>44381</v>
+      </c>
+      <c r="N17" t="n">
         <v>-22111</v>
       </c>
-      <c r="N17" t="n">
-        <v>16.2</v>
+      <c r="O17" t="n">
+        <v>15.43</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260319.xlsx
+++ b/outputs/monitor_xlsx/20260319.xlsx
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2036,6 +2036,165 @@
         <v>15.43</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1680</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8011</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>-3005</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-8634</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-222</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-947</v>
+      </c>
+      <c r="K18" t="n">
+        <v>511</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6038</v>
+      </c>
+      <c r="M18" t="n">
+        <v>29993</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400965</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-3.86</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>581</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F19" t="n">
+        <v>9690</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>2110</v>
+      </c>
+      <c r="H19" t="n">
+        <v>15440</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-118</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1424</v>
+      </c>
+      <c r="K19" t="n">
+        <v>255</v>
+      </c>
+      <c r="L19" t="n">
+        <v>34391</v>
+      </c>
+      <c r="M19" t="n">
+        <v>178230</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-392435</v>
+      </c>
+      <c r="O19" t="n">
+        <v>20.27</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>561</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="F20" t="n">
+        <v>19507</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>-3215</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-13466</v>
+      </c>
+      <c r="I20" t="n">
+        <v>217</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6470</v>
+      </c>
+      <c r="K20" t="n">
+        <v>854</v>
+      </c>
+      <c r="L20" t="n">
+        <v>11597</v>
+      </c>
+      <c r="M20" t="n">
+        <v>51621</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-161227</v>
+      </c>
+      <c r="O20" t="n">
+        <v>12.77</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
